--- a/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times.xlsx
+++ b/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times.xlsx
@@ -413,21 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>pd</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>hopa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>gdpa-100</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>gdpa-200</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>bf</t>
         </is>
@@ -438,13 +448,19 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0003413284383714199</v>
+        <v>0.0001368683949112892</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002619666792452336</v>
+        <v>0.0003360499907284975</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4560358345508576</v>
+        <v>0.0003301798645406961</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0002777300029993057</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4582752680778504</v>
       </c>
     </row>
     <row r="3">
@@ -452,13 +468,19 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0003799166902899742</v>
+        <v>0.0001394066866487265</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0003014316689223051</v>
+        <v>0.0003211833164095879</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3546077561378479</v>
+        <v>0.0002941682934761047</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0002357499673962593</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3540511178970337</v>
       </c>
     </row>
     <row r="4">
@@ -466,13 +488,19 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0003712850343436003</v>
+        <v>0.0001401899103075266</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002817266713827849</v>
+        <v>0.0003370282426476479</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3143586891889572</v>
+        <v>0.0003079382609575987</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.000261054914444685</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.315459703207016</v>
       </c>
     </row>
     <row r="5">
@@ -480,13 +508,19 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0009825183544307948</v>
+        <v>0.0001463733147829771</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0005974982306361198</v>
+        <v>0.0005986049771308898</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3034147179126739</v>
+        <v>0.0008618883974850178</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0008090117573738098</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3047110742330551</v>
       </c>
     </row>
     <row r="6">
@@ -494,13 +528,19 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.003570451801642776</v>
+        <v>0.0001365916430950165</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003299361690878868</v>
+        <v>0.0005681800376623869</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3348790818452835</v>
+        <v>0.002960000038146973</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.002818504963070154</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3350402837991714</v>
       </c>
     </row>
     <row r="7">
@@ -508,13 +548,19 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.009993974985554814</v>
+        <v>0.0001457000151276589</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009737256718799471</v>
+        <v>0.0006715099234133959</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3741119164228439</v>
+        <v>0.009925934663042426</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01000043971464038</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3732976883649826</v>
       </c>
     </row>
     <row r="8">
@@ -522,13 +568,19 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03307399030774832</v>
+        <v>0.0001813033781945705</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03369759494438768</v>
+        <v>0.001610544892027974</v>
       </c>
       <c r="D8" t="n">
-        <v>0.468177964091301</v>
+        <v>0.03553116578608751</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.03609641855582595</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4728059631586075</v>
       </c>
     </row>
     <row r="9">
@@ -536,13 +588,19 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>1.414537314819172</v>
+        <v>0.0001676932629197836</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8470635627955199</v>
+        <v>0.01733521204441786</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3641132539510727</v>
+        <v>0.8621151719521731</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8386285943444818</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3602443265914917</v>
       </c>
     </row>
     <row r="10">
@@ -550,13 +608,19 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.07037876049987972</v>
+        <v>0.0001386115420609713</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06728185413405299</v>
+        <v>0.02534678370691836</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3033003252744675</v>
+        <v>0.06935173191130162</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.06114743678830564</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3005736583471298</v>
       </c>
     </row>
     <row r="11">
@@ -564,13 +628,19 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1239828766416758</v>
+        <v>0.0001478401105850935</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3711445397883654</v>
+        <v>0.03390536530874669</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2524626421928406</v>
+        <v>0.1295336409006268</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3765220335498452</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2494030541181564</v>
       </c>
     </row>
     <row r="12">
@@ -578,13 +648,19 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5615051189996302</v>
+        <v>0.0002434248570352793</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5675653380248695</v>
+        <v>0.1838544829934835</v>
       </c>
       <c r="D12" t="n">
-        <v>0.343082720041275</v>
+        <v>0.562407465511933</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4961658004298806</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3432255566120148</v>
       </c>
     </row>
     <row r="13">
@@ -592,13 +668,19 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>1.224933011168614</v>
+        <v>0.0002096882462501526</v>
       </c>
       <c r="C13" t="n">
-        <v>1.152696136431768</v>
+        <v>0.4118075727764517</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3062128594517708</v>
+        <v>1.216136289797723</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.235375944590196</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3078897991776466</v>
       </c>
     </row>
     <row r="14">
@@ -606,13 +688,19 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>34.22902087188326</v>
+        <v>0.00111155841499567</v>
       </c>
       <c r="C14" t="n">
-        <v>34.02140461932868</v>
+        <v>4.604252429297194</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3110602560639382</v>
+        <v>33.95845279826783</v>
+      </c>
+      <c r="E14" t="n">
+        <v>34.07347883541137</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3179593506455421</v>
       </c>
     </row>
     <row r="15">
@@ -620,13 +708,19 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>3.997588220369071</v>
+        <v>0.001241768207401037</v>
       </c>
       <c r="C15" t="n">
-        <v>4.274552980661392</v>
+        <v>4.060249921772629</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2709017172455788</v>
+        <v>3.929141035499051</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.349990327386186</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2873890450596809</v>
       </c>
     </row>
     <row r="16">
@@ -634,13 +728,19 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>1.326930256485939</v>
+        <v>0.0004861684516072273</v>
       </c>
       <c r="C16" t="n">
-        <v>1.317449635863304</v>
+        <v>2.651829698085785</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7354775729775429</v>
+        <v>1.269957534074783</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.335782067775726</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7358956974744797</v>
       </c>
     </row>
     <row r="17">
@@ -648,13 +748,19 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.7615489342808723</v>
+        <v>0.0001680465135723352</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8099828904867172</v>
+        <v>0.7649391439557075</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6013017490506172</v>
+        <v>0.7289154240489006</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8013824424147606</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.6097133451700211</v>
       </c>
     </row>
     <row r="18">
@@ -662,13 +768,19 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.6258629426360131</v>
+        <v>0.0001090167462825775</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7576155626773834</v>
+        <v>0.3787030926346779</v>
       </c>
       <c r="D18" t="n">
-        <v>1.597453631460667</v>
+        <v>0.5777967315912247</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6996280667185784</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.753784028291702</v>
       </c>
     </row>
     <row r="19">
@@ -676,13 +788,19 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5938520288467407</v>
+        <v>8.451004512608051e-05</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9741957724094391</v>
+        <v>0.2227823839336634</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5073037049174309</v>
+        <v>0.5614343695342541</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9714649985730648</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5045707741379738</v>
       </c>
     </row>
     <row r="20">
@@ -690,13 +808,19 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>6.123412573635578</v>
+        <v>9.882830083370209e-05</v>
       </c>
       <c r="C20" t="n">
-        <v>6.493164838552475</v>
+        <v>0.1684457725286484</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5839696159958839</v>
+        <v>6.072406358420849</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6.443742446005344</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5828448966145515</v>
       </c>
     </row>
     <row r="21">
@@ -704,13 +828,19 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.5797276556491852</v>
+        <v>8.207998238503934e-05</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8053238189220429</v>
+        <v>0.1420872388035059</v>
       </c>
       <c r="D21" t="n">
-        <v>0.406132196187973</v>
+        <v>0.5734261178970337</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.800180156826973</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4042882332205772</v>
       </c>
     </row>
   </sheetData>

--- a/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times.xlsx
+++ b/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,15 +429,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>gdpa-prio</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>gdpa-100</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>gdpa-200</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>bf</t>
         </is>
@@ -454,12 +459,15 @@
         <v>0.0003360499907284975</v>
       </c>
       <c r="D2" t="n">
+        <v>0.0003416150342673063</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.0003301798645406961</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.0002777300029993057</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.4582752680778504</v>
       </c>
     </row>
@@ -474,12 +482,15 @@
         <v>0.0003211833164095879</v>
       </c>
       <c r="D3" t="n">
+        <v>0.0005295366048812866</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.0002941682934761047</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.0002357499673962593</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.3540511178970337</v>
       </c>
     </row>
@@ -494,12 +505,15 @@
         <v>0.0003370282426476479</v>
       </c>
       <c r="D4" t="n">
+        <v>0.000475651565939188</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.0003079382609575987</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.000261054914444685</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.315459703207016</v>
       </c>
     </row>
@@ -514,12 +528,15 @@
         <v>0.0005986049771308898</v>
       </c>
       <c r="D5" t="n">
+        <v>0.0004669700469821692</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.0008618883974850178</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.0008090117573738098</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.3047110742330551</v>
       </c>
     </row>
@@ -534,12 +551,15 @@
         <v>0.0005681800376623869</v>
       </c>
       <c r="D6" t="n">
+        <v>0.0009011666849255562</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.002960000038146973</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.002818504963070154</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.3350402837991714</v>
       </c>
     </row>
@@ -554,12 +574,15 @@
         <v>0.0006715099234133959</v>
       </c>
       <c r="D7" t="n">
+        <v>0.001730554969981313</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.009925934663042426</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.01000043971464038</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.3732976883649826</v>
       </c>
     </row>
@@ -574,12 +597,15 @@
         <v>0.001610544892027974</v>
       </c>
       <c r="D8" t="n">
+        <v>0.002285326505079865</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.03553116578608751</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>0.03609641855582595</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>0.4728059631586075</v>
       </c>
     </row>
@@ -594,12 +620,15 @@
         <v>0.01733521204441786</v>
       </c>
       <c r="D9" t="n">
+        <v>0.01040290514938533</v>
+      </c>
+      <c r="E9" t="n">
         <v>0.8621151719521731</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0.8386285943444818</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>0.3602443265914917</v>
       </c>
     </row>
@@ -614,12 +643,15 @@
         <v>0.02534678370691836</v>
       </c>
       <c r="D10" t="n">
+        <v>0.01618385492824018</v>
+      </c>
+      <c r="E10" t="n">
         <v>0.06935173191130162</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>0.06114743678830564</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.3005736583471298</v>
       </c>
     </row>
@@ -634,12 +666,15 @@
         <v>0.03390536530874669</v>
       </c>
       <c r="D11" t="n">
+        <v>0.03147003975696862</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.1295336409006268</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0.3765220335498452</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.2494030541181564</v>
       </c>
     </row>
@@ -654,12 +689,15 @@
         <v>0.1838544829934835</v>
       </c>
       <c r="D12" t="n">
+        <v>0.1245417342055589</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.562407465511933</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0.4961658004298806</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>0.3432255566120148</v>
       </c>
     </row>
@@ -674,12 +712,15 @@
         <v>0.4118075727764517</v>
       </c>
       <c r="D13" t="n">
+        <v>1.004606450535357</v>
+      </c>
+      <c r="E13" t="n">
         <v>1.216136289797723</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>1.235375944590196</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>0.3078897991776466</v>
       </c>
     </row>
@@ -694,12 +735,15 @@
         <v>4.604252429297194</v>
       </c>
       <c r="D14" t="n">
+        <v>3.319734947495162</v>
+      </c>
+      <c r="E14" t="n">
         <v>33.95845279826783</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>34.07347883541137</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>0.3179593506455421</v>
       </c>
     </row>
@@ -714,12 +758,15 @@
         <v>4.060249921772629</v>
       </c>
       <c r="D15" t="n">
+        <v>3.632888285499066</v>
+      </c>
+      <c r="E15" t="n">
         <v>3.929141035499051</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>4.349990327386186</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>0.2873890450596809</v>
       </c>
     </row>
@@ -734,12 +781,15 @@
         <v>2.651829698085785</v>
       </c>
       <c r="D16" t="n">
+        <v>1.194969080090523</v>
+      </c>
+      <c r="E16" t="n">
         <v>1.269957534074783</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>1.335782067775726</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.7358956974744797</v>
       </c>
     </row>
@@ -754,12 +804,15 @@
         <v>0.7649391439557075</v>
       </c>
       <c r="D17" t="n">
+        <v>0.3480069254338741</v>
+      </c>
+      <c r="E17" t="n">
         <v>0.7289154240489006</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>0.8013824424147606</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>0.6097133451700211</v>
       </c>
     </row>
@@ -774,12 +827,15 @@
         <v>0.3787030926346779</v>
       </c>
       <c r="D18" t="n">
+        <v>0.1953749577701092</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.5777967315912247</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>0.6996280667185784</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>1.753784028291702</v>
       </c>
     </row>
@@ -794,12 +850,15 @@
         <v>0.2227823839336634</v>
       </c>
       <c r="D19" t="n">
+        <v>0.1585748028755188</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.5614343695342541</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>0.9714649985730648</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>0.5045707741379738</v>
       </c>
     </row>
@@ -814,12 +873,15 @@
         <v>0.1684457725286484</v>
       </c>
       <c r="D20" t="n">
+        <v>0.09728527635335922</v>
+      </c>
+      <c r="E20" t="n">
         <v>6.072406358420849</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>6.443742446005344</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>0.5828448966145515</v>
       </c>
     </row>
@@ -834,12 +896,15 @@
         <v>0.1420872388035059</v>
       </c>
       <c r="D21" t="n">
+        <v>0.0976408414542675</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.5734261178970337</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>0.800180156826973</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>0.4042882332205772</v>
       </c>
     </row>

--- a/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times.xlsx
+++ b/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>gdpa-ms</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>bf</t>
         </is>
       </c>
@@ -468,6 +473,9 @@
         <v>0.0002777300029993057</v>
       </c>
       <c r="G2" t="n">
+        <v>0.0005483967438340187</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.4582752680778504</v>
       </c>
     </row>
@@ -491,6 +499,9 @@
         <v>0.0002357499673962593</v>
       </c>
       <c r="G3" t="n">
+        <v>0.0005519283376634121</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.3540511178970337</v>
       </c>
     </row>
@@ -514,6 +525,9 @@
         <v>0.000261054914444685</v>
       </c>
       <c r="G4" t="n">
+        <v>0.000723953228443861</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.315459703207016</v>
       </c>
     </row>
@@ -537,6 +551,9 @@
         <v>0.0008090117573738098</v>
       </c>
       <c r="G5" t="n">
+        <v>0.002200389998033643</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.3047110742330551</v>
       </c>
     </row>
@@ -560,6 +577,9 @@
         <v>0.002818504963070154</v>
       </c>
       <c r="G6" t="n">
+        <v>0.02261634830385446</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.3350402837991714</v>
       </c>
     </row>
@@ -583,6 +603,9 @@
         <v>0.01000043971464038</v>
       </c>
       <c r="G7" t="n">
+        <v>0.02381413975730538</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.3732976883649826</v>
       </c>
     </row>
@@ -606,6 +629,9 @@
         <v>0.03609641855582595</v>
       </c>
       <c r="G8" t="n">
+        <v>0.06260479481890797</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.4728059631586075</v>
       </c>
     </row>
@@ -629,6 +655,9 @@
         <v>0.8386285943444818</v>
       </c>
       <c r="G9" t="n">
+        <v>0.8339146154653281</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.3602443265914917</v>
       </c>
     </row>
@@ -652,6 +681,9 @@
         <v>0.06114743678830564</v>
       </c>
       <c r="G10" t="n">
+        <v>0.1941089734714478</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.3005736583471298</v>
       </c>
     </row>
@@ -675,6 +707,9 @@
         <v>0.3765220335498452</v>
       </c>
       <c r="G11" t="n">
+        <v>0.5128496505599469</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.2494030541181564</v>
       </c>
     </row>
@@ -698,6 +733,9 @@
         <v>0.4961658004298806</v>
       </c>
       <c r="G12" t="n">
+        <v>0.9833970176801086</v>
+      </c>
+      <c r="H12" t="n">
         <v>0.3432255566120148</v>
       </c>
     </row>
@@ -721,6 +759,9 @@
         <v>1.235375944590196</v>
       </c>
       <c r="G13" t="n">
+        <v>3.807213165964931</v>
+      </c>
+      <c r="H13" t="n">
         <v>0.3078897991776466</v>
       </c>
     </row>
@@ -744,6 +785,9 @@
         <v>34.07347883541137</v>
       </c>
       <c r="G14" t="n">
+        <v>36.60225742855109</v>
+      </c>
+      <c r="H14" t="n">
         <v>0.3179593506455421</v>
       </c>
     </row>
@@ -767,6 +811,9 @@
         <v>4.349990327386186</v>
       </c>
       <c r="G15" t="n">
+        <v>7.364517458835617</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.2873890450596809</v>
       </c>
     </row>
@@ -790,6 +837,9 @@
         <v>1.335782067775726</v>
       </c>
       <c r="G16" t="n">
+        <v>3.911061153113842</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.7358956974744797</v>
       </c>
     </row>
@@ -813,6 +863,9 @@
         <v>0.8013824424147606</v>
       </c>
       <c r="G17" t="n">
+        <v>4.852173634469509</v>
+      </c>
+      <c r="H17" t="n">
         <v>0.6097133451700211</v>
       </c>
     </row>
@@ -836,6 +889,9 @@
         <v>0.6996280667185784</v>
       </c>
       <c r="G18" t="n">
+        <v>17.9088856574893</v>
+      </c>
+      <c r="H18" t="n">
         <v>1.753784028291702</v>
       </c>
     </row>
@@ -859,6 +915,9 @@
         <v>0.9714649985730648</v>
       </c>
       <c r="G19" t="n">
+        <v>3.410328145623207</v>
+      </c>
+      <c r="H19" t="n">
         <v>0.5045707741379738</v>
       </c>
     </row>
@@ -882,6 +941,9 @@
         <v>6.443742446005344</v>
       </c>
       <c r="G20" t="n">
+        <v>12.72865613102913</v>
+      </c>
+      <c r="H20" t="n">
         <v>0.5828448966145515</v>
       </c>
     </row>
@@ -905,6 +967,9 @@
         <v>0.800180156826973</v>
       </c>
       <c r="G21" t="n">
+        <v>10.22447470843792</v>
+      </c>
+      <c r="H21" t="n">
         <v>0.4042882332205772</v>
       </c>
     </row>

--- a/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times.xlsx
+++ b/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>gdpa-ms</t>
+          <t>gdpa-500</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -467,13 +467,13 @@
         <v>0.0003416150342673063</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003301798645406961</v>
+        <v>0.0005095131509006023</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002777300029993057</v>
+        <v>0.0004423550423234701</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0005483967438340187</v>
+        <v>0.0005191765818744898</v>
       </c>
       <c r="H2" t="n">
         <v>0.4582752680778504</v>
@@ -493,13 +493,13 @@
         <v>0.0005295366048812866</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002941682934761047</v>
+        <v>0.0006020266376435757</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0002357499673962593</v>
+        <v>0.0004342267103493214</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005519283376634121</v>
+        <v>0.0003772150166332722</v>
       </c>
       <c r="H3" t="n">
         <v>0.3540511178970337</v>
@@ -519,13 +519,13 @@
         <v>0.000475651565939188</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003079382609575987</v>
+        <v>0.0005282367207109928</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000261054914444685</v>
+        <v>0.0004220350552350283</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000723953228443861</v>
+        <v>0.0004140883032232523</v>
       </c>
       <c r="H4" t="n">
         <v>0.315459703207016</v>
@@ -545,13 +545,13 @@
         <v>0.0004669700469821692</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0008618883974850178</v>
+        <v>0.003011890146881342</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0008090117573738098</v>
+        <v>0.002882975013926625</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002200389998033643</v>
+        <v>0.002849804908037186</v>
       </c>
       <c r="H5" t="n">
         <v>0.3047110742330551</v>
@@ -571,13 +571,13 @@
         <v>0.0009011666849255562</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002960000038146973</v>
+        <v>0.02061164035461843</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002818504963070154</v>
+        <v>0.01963330503553152</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02261634830385446</v>
+        <v>0.01952877149917185</v>
       </c>
       <c r="H6" t="n">
         <v>0.3350402837991714</v>
@@ -597,13 +597,13 @@
         <v>0.001730554969981313</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009925934663042426</v>
+        <v>0.06939669345505535</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01000043971464038</v>
+        <v>0.06639822180382908</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02381413975730538</v>
+        <v>0.06587546180002392</v>
       </c>
       <c r="H7" t="n">
         <v>0.3732976883649826</v>
@@ -623,13 +623,13 @@
         <v>0.002285326505079865</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03553116578608751</v>
+        <v>0.05126201952807605</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03609641855582595</v>
+        <v>0.04889098497107625</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06260479481890797</v>
+        <v>0.04821279509924352</v>
       </c>
       <c r="H8" t="n">
         <v>0.4728059631586075</v>
@@ -649,13 +649,13 @@
         <v>0.01040290514938533</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8621151719521731</v>
+        <v>0.8520767791382968</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8386285943444818</v>
+        <v>0.8216597569733858</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8339146154653281</v>
+        <v>0.8098553357459605</v>
       </c>
       <c r="H9" t="n">
         <v>0.3602443265914917</v>
@@ -675,13 +675,13 @@
         <v>0.01618385492824018</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06935173191130162</v>
+        <v>0.2429448819160461</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06114743678830564</v>
+        <v>0.2164601116813719</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1941089734714478</v>
+        <v>0.253818922424689</v>
       </c>
       <c r="H10" t="n">
         <v>0.3005736583471298</v>
@@ -701,13 +701,13 @@
         <v>0.03147003975696862</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1295336409006268</v>
+        <v>0.8011621759738773</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3765220335498452</v>
+        <v>0.7639709469955415</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5128496505599469</v>
+        <v>0.744724514465779</v>
       </c>
       <c r="H11" t="n">
         <v>0.2494030541181564</v>
@@ -727,13 +727,13 @@
         <v>0.1245417342055589</v>
       </c>
       <c r="E12" t="n">
-        <v>0.562407465511933</v>
+        <v>1.062302935207263</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4961658004298806</v>
+        <v>1.086989105213434</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9833970176801086</v>
+        <v>1.644784434093162</v>
       </c>
       <c r="H12" t="n">
         <v>0.3432255566120148</v>
@@ -753,13 +753,13 @@
         <v>1.004606450535357</v>
       </c>
       <c r="E13" t="n">
-        <v>1.216136289797723</v>
+        <v>5.741593129588291</v>
       </c>
       <c r="F13" t="n">
-        <v>1.235375944590196</v>
+        <v>6.875290413228795</v>
       </c>
       <c r="G13" t="n">
-        <v>3.807213165964931</v>
+        <v>22.6613404744491</v>
       </c>
       <c r="H13" t="n">
         <v>0.3078897991776466</v>
@@ -779,13 +779,13 @@
         <v>3.319734947495162</v>
       </c>
       <c r="E14" t="n">
-        <v>33.95845279826783</v>
+        <v>4.903037796588615</v>
       </c>
       <c r="F14" t="n">
-        <v>34.07347883541137</v>
+        <v>5.26292245304212</v>
       </c>
       <c r="G14" t="n">
-        <v>36.60225742855109</v>
+        <v>4.060593439219519</v>
       </c>
       <c r="H14" t="n">
         <v>0.3179593506455421</v>
@@ -805,13 +805,13 @@
         <v>3.632888285499066</v>
       </c>
       <c r="E15" t="n">
-        <v>3.929141035499051</v>
+        <v>23.22646875234321</v>
       </c>
       <c r="F15" t="n">
-        <v>4.349990327386186</v>
+        <v>25.76219057002105</v>
       </c>
       <c r="G15" t="n">
-        <v>7.364517458835617</v>
+        <v>21.41567161802202</v>
       </c>
       <c r="H15" t="n">
         <v>0.2873890450596809</v>
@@ -831,13 +831,13 @@
         <v>1.194969080090523</v>
       </c>
       <c r="E16" t="n">
-        <v>1.269957534074783</v>
+        <v>2.373917600214481</v>
       </c>
       <c r="F16" t="n">
-        <v>1.335782067775726</v>
+        <v>3.314659405350685</v>
       </c>
       <c r="G16" t="n">
-        <v>3.911061153113842</v>
+        <v>4.024363815784454</v>
       </c>
       <c r="H16" t="n">
         <v>0.7358956974744797</v>
@@ -857,13 +857,13 @@
         <v>0.3480069254338741</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7289154240489006</v>
+        <v>1.614987845327705</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8013824424147606</v>
+        <v>3.426560927219689</v>
       </c>
       <c r="G17" t="n">
-        <v>4.852173634469509</v>
+        <v>3.046602583676576</v>
       </c>
       <c r="H17" t="n">
         <v>0.6097133451700211</v>
@@ -883,13 +883,13 @@
         <v>0.1953749577701092</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5777967315912247</v>
+        <v>4.559379985332489</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6996280667185784</v>
+        <v>11.34180482149124</v>
       </c>
       <c r="G18" t="n">
-        <v>17.9088856574893</v>
+        <v>11.80438156723976</v>
       </c>
       <c r="H18" t="n">
         <v>1.753784028291702</v>
@@ -909,13 +909,13 @@
         <v>0.1585748028755188</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5614343695342541</v>
+        <v>3.098077181577683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9714649985730648</v>
+        <v>6.003257108926773</v>
       </c>
       <c r="G19" t="n">
-        <v>3.410328145623207</v>
+        <v>8.894302667975426</v>
       </c>
       <c r="H19" t="n">
         <v>0.5045707741379738</v>
@@ -935,13 +935,13 @@
         <v>0.09728527635335922</v>
       </c>
       <c r="E20" t="n">
-        <v>6.072406358420849</v>
+        <v>5.859622557163238</v>
       </c>
       <c r="F20" t="n">
-        <v>6.443742446005344</v>
+        <v>8.889899633526802</v>
       </c>
       <c r="G20" t="n">
-        <v>12.72865613102913</v>
+        <v>11.30967647135258</v>
       </c>
       <c r="H20" t="n">
         <v>0.5828448966145515</v>
@@ -961,13 +961,13 @@
         <v>0.0976408414542675</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5734261178970337</v>
+        <v>2.742126104831696</v>
       </c>
       <c r="F21" t="n">
-        <v>0.800180156826973</v>
+        <v>3.711711451411247</v>
       </c>
       <c r="G21" t="n">
-        <v>10.22447470843792</v>
+        <v>7.205381342768669</v>
       </c>
       <c r="H21" t="n">
         <v>0.4042882332205772</v>

--- a/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times.xlsx
+++ b/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>bf</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>bf-seq</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -478,6 +483,9 @@
       <c r="H2" t="n">
         <v>0.4582752680778504</v>
       </c>
+      <c r="I2" t="n">
+        <v>1.257664906829596</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -504,6 +512,9 @@
       <c r="H3" t="n">
         <v>0.3540511178970337</v>
       </c>
+      <c r="I3" t="n">
+        <v>0.8568585384264589</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -530,6 +541,9 @@
       <c r="H4" t="n">
         <v>0.315459703207016</v>
       </c>
+      <c r="I4" t="n">
+        <v>0.6752389370650053</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -556,6 +570,9 @@
       <c r="H5" t="n">
         <v>0.3047110742330551</v>
       </c>
+      <c r="I5" t="n">
+        <v>0.8894357065856456</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -582,6 +599,9 @@
       <c r="H6" t="n">
         <v>0.3350402837991714</v>
       </c>
+      <c r="I6" t="n">
+        <v>0.4635359591990709</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -608,6 +628,9 @@
       <c r="H7" t="n">
         <v>0.3732976883649826</v>
       </c>
+      <c r="I7" t="n">
+        <v>0.6848957301676273</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -634,6 +657,9 @@
       <c r="H8" t="n">
         <v>0.4728059631586075</v>
       </c>
+      <c r="I8" t="n">
+        <v>0.7376334971189499</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -660,6 +686,9 @@
       <c r="H9" t="n">
         <v>0.3602443265914917</v>
       </c>
+      <c r="I9" t="n">
+        <v>0.5673317218571902</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -686,6 +715,9 @@
       <c r="H10" t="n">
         <v>0.3005736583471298</v>
       </c>
+      <c r="I10" t="n">
+        <v>0.2732098084688186</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -712,6 +744,9 @@
       <c r="H11" t="n">
         <v>0.2494030541181564</v>
       </c>
+      <c r="I11" t="n">
+        <v>0.2017023532092571</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -738,6 +773,9 @@
       <c r="H12" t="n">
         <v>0.3432255566120148</v>
       </c>
+      <c r="I12" t="n">
+        <v>0.2878326430916786</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -764,6 +802,9 @@
       <c r="H13" t="n">
         <v>0.3078897991776466</v>
       </c>
+      <c r="I13" t="n">
+        <v>0.2834323615580797</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -790,6 +831,9 @@
       <c r="H14" t="n">
         <v>0.3179593506455421</v>
       </c>
+      <c r="I14" t="n">
+        <v>0.3143969346210361</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -816,6 +860,9 @@
       <c r="H15" t="n">
         <v>0.2873890450596809</v>
       </c>
+      <c r="I15" t="n">
+        <v>0.3236230204999447</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -842,6 +889,9 @@
       <c r="H16" t="n">
         <v>0.7358956974744797</v>
       </c>
+      <c r="I16" t="n">
+        <v>1.165184846296907</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -868,6 +918,9 @@
       <c r="H17" t="n">
         <v>0.6097133451700211</v>
       </c>
+      <c r="I17" t="n">
+        <v>1.282050467282534</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -894,6 +947,9 @@
       <c r="H18" t="n">
         <v>1.753784028291702</v>
       </c>
+      <c r="I18" t="n">
+        <v>1.140549317598343</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -920,6 +976,9 @@
       <c r="H19" t="n">
         <v>0.5045707741379738</v>
       </c>
+      <c r="I19" t="n">
+        <v>1.291982241794467</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -946,6 +1005,9 @@
       <c r="H20" t="n">
         <v>0.5828448966145515</v>
       </c>
+      <c r="I20" t="n">
+        <v>1.679792297258973</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -971,6 +1033,9 @@
       </c>
       <c r="H21" t="n">
         <v>0.4042882332205772</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.109471996054053</v>
       </c>
     </row>
   </sheetData>
